--- a/02-VALUATION/M08/bus311-valuation-m08-l01-npv-practice.xlsx
+++ b/02-VALUATION/M08/bus311-valuation-m08-l01-npv-practice.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/BUS311 Corporate Finance/BME - FA25- Teaching Materials - Brealey/Chapter 8 -Net Present Value/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/58a91613f0104f47/EC_Teaching/BUS311 Corporate Finance_current/FA25- Teaching Materials - Brealey/Chapter 8 -Net Present Value/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{8426469E-2962-461D-8E87-27E1F9BB1A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF8D7EB-46D0-4CAF-9358-BD734540D9A3}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{8426469E-2962-461D-8E87-27E1F9BB1A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03A37488-63EC-8645-8813-2B5977D6CB5E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{A5A99A8F-0BAD-4153-844B-017F01CA73DA}"/>
+    <workbookView xWindow="1420" yWindow="1340" windowWidth="23880" windowHeight="19200" activeTab="5" xr2:uid="{A5A99A8F-0BAD-4153-844B-017F01CA73DA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Question #1" sheetId="2" r:id="rId1"/>
-    <sheet name="Question#2" sheetId="1" r:id="rId2"/>
+    <sheet name="Office NPV" sheetId="3" r:id="rId1"/>
+    <sheet name="NPV w Salvage Value" sheetId="4" r:id="rId2"/>
+    <sheet name="IRR- Slide 13" sheetId="5" r:id="rId3"/>
+    <sheet name="Profitabiliy Index" sheetId="6" r:id="rId4"/>
+    <sheet name="PayBack Period-Slide" sheetId="7" r:id="rId5"/>
+    <sheet name="Question #1" sheetId="2" r:id="rId6"/>
+    <sheet name="Question#2" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>NP-30</t>
   </si>
@@ -87,9 +92,6 @@
     <t>Profitability Index</t>
   </si>
   <si>
-    <t>Net Present Value</t>
-  </si>
-  <si>
     <t>Which project would you recommend?</t>
   </si>
   <si>
@@ -148,13 +150,86 @@
   </si>
   <si>
     <t>Project 2</t>
+  </si>
+  <si>
+    <t>Cost of Building</t>
+  </si>
+  <si>
+    <t>Sale Price (Year 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Capital </t>
+  </si>
+  <si>
+    <t>Initial Cost</t>
+  </si>
+  <si>
+    <t>Inflows</t>
+  </si>
+  <si>
+    <t>Outflows</t>
+  </si>
+  <si>
+    <t>Net Flow</t>
+  </si>
+  <si>
+    <t>Salvage</t>
+  </si>
+  <si>
+    <t>Cost of Capital</t>
+  </si>
+  <si>
+    <t>PV of Cashflows</t>
+  </si>
+  <si>
+    <t>NPV of Project</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Cash Flow</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>PV of CFs</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Gamma</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Yearly Cashflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payback </t>
+  </si>
+  <si>
+    <t>Project Net Present Value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="10">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -165,7 +240,7 @@
     <numFmt numFmtId="167" formatCode="0.000%"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,8 +351,40 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,8 +421,20 @@
         <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -475,13 +594,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -558,6 +706,35 @@
     <xf numFmtId="168" fontId="10" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -582,6 +759,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -900,29 +1081,351 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F306023-1183-F54F-86E3-558F92753D38}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DB6E15-A5D7-604A-9B2D-8C2FA858B4DA}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="54">
+        <v>-350000</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+    </row>
+    <row r="4" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+    </row>
+    <row r="5" spans="1:5" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+    </row>
+    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+    </row>
+    <row r="7" spans="1:5" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="58"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" t="e">
+        <f ca="1">_xlfn.FORMULATEXT(B12)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="60"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFD8D9C-0CDB-CB43-ABD3-6A2E77B5FD07}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="61"/>
+    </row>
+    <row r="2" spans="1:3" ht="25" x14ac:dyDescent="0.2">
+      <c r="A2" s="62">
+        <v>0</v>
+      </c>
+      <c r="B2" s="63">
+        <v>-375000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A3" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="63">
+        <v>25000</v>
+      </c>
+      <c r="C3" s="64"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" x14ac:dyDescent="0.2">
+      <c r="A4" s="62">
+        <v>2</v>
+      </c>
+      <c r="B4" s="63">
+        <v>25000</v>
+      </c>
+      <c r="C4" s="64"/>
+    </row>
+    <row r="5" spans="1:3" ht="25" x14ac:dyDescent="0.2">
+      <c r="A5" s="62">
+        <v>3</v>
+      </c>
+      <c r="B5" s="63">
+        <v>475000</v>
+      </c>
+      <c r="C5" s="64"/>
+    </row>
+    <row r="7" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A7" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="65"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E11E3AC4-5CF4-8342-8981-641F40633AF4}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="55">
+        <v>200</v>
+      </c>
+      <c r="C2" s="55">
+        <v>120</v>
+      </c>
+      <c r="E2" s="67"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="55">
+        <v>500</v>
+      </c>
+      <c r="C3" s="55">
+        <v>230</v>
+      </c>
+      <c r="E3" s="67"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="55">
+        <v>100</v>
+      </c>
+      <c r="C4" s="55">
+        <v>75</v>
+      </c>
+      <c r="E4" s="67"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="55">
+        <v>400</v>
+      </c>
+      <c r="C5" s="55">
+        <v>140</v>
+      </c>
+      <c r="E5" s="67"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA4F8A5-08E2-124C-B491-BDA05226B59A}">
+  <dimension ref="A2:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="67"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0587A5-68AF-49D2-9A1E-2801C9A977A1}">
   <dimension ref="A1:Z35"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" customWidth="1"/>
-    <col min="5" max="8" width="12.1796875" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" customWidth="1"/>
-    <col min="10" max="15" width="12.1796875" customWidth="1"/>
-    <col min="16" max="16" width="14.26953125" customWidth="1"/>
-    <col min="17" max="26" width="12.1796875" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="8" width="12.1640625" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="15" width="12.1640625" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="26" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="C1" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="31" x14ac:dyDescent="0.35">
+      <c r="B2" s="32" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" ht="31" x14ac:dyDescent="0.7">
-      <c r="B2" s="32" t="s">
-        <v>22</v>
       </c>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
@@ -931,29 +1434,29 @@
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
     </row>
-    <row r="3" spans="1:26" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:26" ht="19" x14ac:dyDescent="0.25">
       <c r="B3" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+    </row>
+    <row r="6" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="35"/>
       <c r="B6" s="36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="36">
         <v>0</v>
@@ -992,9 +1495,9 @@
       <c r="Y6" s="35"/>
       <c r="Z6" s="35"/>
     </row>
-    <row r="7" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37">
@@ -1015,9 +1518,9 @@
       <c r="J7" s="38"/>
       <c r="Q7" s="38"/>
     </row>
-    <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="37">
         <v>-1500000</v>
@@ -1040,9 +1543,9 @@
       <c r="P8" s="39"/>
       <c r="Q8" s="38"/>
     </row>
-    <row r="9" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="41"/>
@@ -1053,9 +1556,9 @@
       <c r="P9" s="39"/>
       <c r="Q9" s="38"/>
     </row>
-    <row r="10" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="41"/>
@@ -1066,7 +1569,7 @@
       <c r="P10" s="42"/>
       <c r="Q10" s="38"/>
     </row>
-    <row r="11" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="43"/>
       <c r="C11" s="44"/>
       <c r="D11" s="44"/>
@@ -1077,9 +1580,9 @@
       <c r="P11" s="39"/>
       <c r="Q11" s="38"/>
     </row>
-    <row r="12" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="46">
         <v>0.08</v>
@@ -1092,53 +1595,53 @@
       <c r="P12" s="39"/>
       <c r="Q12" s="38"/>
     </row>
-    <row r="13" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" s="47"/>
       <c r="Q13" s="38"/>
     </row>
-    <row r="14" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B14" s="45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="48"/>
     </row>
-    <row r="15" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="45"/>
       <c r="C15" s="49"/>
     </row>
-    <row r="16" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="50"/>
     </row>
-    <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="45"/>
       <c r="C17" s="49"/>
     </row>
-    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B18" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="51"/>
+    </row>
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="51"/>
-    </row>
-    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
+      <c r="B21" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+    </row>
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B22" s="36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="36">
         <v>0</v>
@@ -1159,9 +1662,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B23" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37">
@@ -1180,9 +1683,9 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B24" s="31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="37">
         <v>-250000</v>
@@ -1203,9 +1706,9 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B25" s="40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
@@ -1214,9 +1717,9 @@
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
     </row>
-    <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B26" s="40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
@@ -1225,44 +1728,44 @@
       <c r="G26" s="41"/>
       <c r="H26" s="41"/>
     </row>
-    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B28" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="46">
         <v>0.08</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="C29" s="47"/>
     </row>
-    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B30" s="45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="48"/>
     </row>
-    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B31" s="45"/>
       <c r="C31" s="49"/>
     </row>
-    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="50"/>
     </row>
-    <row r="33" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B33" s="45"/>
       <c r="C33" s="49"/>
     </row>
-    <row r="34" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B34" s="45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="51"/>
     </row>
-    <row r="35" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="C35" s="43"/>
     </row>
   </sheetData>
@@ -1274,28 +1777,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5142316-9F3C-45E7-B810-C0517DD17EF4}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
@@ -1306,7 +1809,7 @@
       </c>
       <c r="E2" s="8"/>
     </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="9" t="s">
         <v>2</v>
@@ -1319,7 +1822,7 @@
       </c>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="9" t="s">
         <v>3</v>
@@ -1332,7 +1835,7 @@
       </c>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="9" t="s">
         <v>4</v>
@@ -1347,7 +1850,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="9" t="s">
         <v>5</v>
@@ -1362,7 +1865,7 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="9" t="s">
         <v>6</v>
@@ -1377,7 +1880,7 @@
       </c>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="9" t="s">
         <v>7</v>
@@ -1392,14 +1895,14 @@
       </c>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
       <c r="C9" s="13"/>
       <c r="D9" s="14"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="9" t="s">
         <v>8</v>
@@ -1410,23 +1913,23 @@
       </c>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="19"/>
       <c r="D11" s="18"/>
       <c r="E11" s="20"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C13" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-    </row>
-    <row r="14" spans="1:5" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C13" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+    </row>
+    <row r="14" spans="1:5" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>0</v>
@@ -1435,10 +1938,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1449,7 +1952,7 @@
       <c r="D15" s="26"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1460,23 +1963,23 @@
       <c r="D16" s="22"/>
       <c r="E16" s="21"/>
     </row>
-    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="21"/>
     </row>
-    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
